--- a/jira/jiraTickets.xlsx
+++ b/jira/jiraTickets.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Automatic Firmware Update for Printer Fleet</t>
+          <t>Enable Secure Boot Support in Firmware</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -533,42 +533,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Update Management</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement automatic firmware update capability across all managed printers in the fleet.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ensures printers are always running the latest firmware, reducing security risks and improving reliability.</t>
+          <t>Enhances platform security by preventing unauthorized code execution at boot time.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Minimizes manual intervention, decreases downtime, and enhances overall fleet security.</t>
+          <t>Reduces risk of malware and unauthorized access, meeting enterprise security requirements.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should not need to manually check or initiate firmware updates.</t>
+          <t>System should boot securely and transparently for end users.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>All managed printers within enterprise environments.</t>
+          <t>Implement Secure Boot verification in firmware for all supported hardware platforms.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Automatic updates enabled for 90% of printers.</t>
+          <t>Secure Boot enabled and verified on all test platforms.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Achieve 100% automatic update coverage for managed printers.</t>
+          <t>100% Secure Boot coverage for all Victoria-supported devices.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Printer management software; network connectivity; firmware update server</t>
+          <t>Firmware cryptographic libraries; hardware TPM support</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IT Operations; Firmware Engineering; Security Team</t>
+          <t>Platform Security Team; Hardware Engineering</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -593,25 +593,25 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
+          <t>SCRUM-25418</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25418</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>{"errorMessages":["You do not have permission to create issues in this project."],"errors":{}}</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Add Support for Secure Print Release</t>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -621,42 +621,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Update Process</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Introduce secure print release functionality requiring user authentication before printing.</t>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Protects sensitive documents from unauthorized access and reduces waste.</t>
+          <t>Ensures business continuity and reduces impact on end users during firmware maintenance.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Improves document security and compliance with enterprise privacy standards.</t>
+          <t>Faster updates, less disruption, improved user satisfaction.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Users must authenticate at the device before their print job is released.</t>
+          <t>Users should experience minimal interruption during firmware updates.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>All printers with badge reader or PIN entry capability.</t>
+          <t>Update firmware process logic to reduce downtime across all Victoria platforms.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Secure print release available on 80% of devices.</t>
+          <t>Firmware update downtime reduced by at least 50% compared to previous release.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Secure print release on all enterprise printers.</t>
+          <t>Achieve less than 2 minutes downtime per update.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Authentication system; badge reader hardware; firmware integration</t>
+          <t>Firmware update subsystem; platform power management</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Security Team; Hardware Engineering; Firmware Team</t>
+          <t>Firmware Engineering; QA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -692,59 +692,59 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{"errorMessages":["You do not have permission to create issues in this project."],"errors":{}}</t>
+          <t>{"errorMessages":[],"errors":{"labels":"The label 'Update Process' can't contain spaces."}}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Improve Printer Boot Time</t>
+          <t>Add Multi-Language Support to Firmware UI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
+          <t>Carlos Ruiz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Optimize firmware to reduce printer boot time by at least 20%.</t>
+          <t>Integrate multi-language capabilities into the firmware user interface.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Faster boot times improve user productivity and reduce frustration.</t>
+          <t>Expands market reach and improves accessibility for global users.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enhanced user experience and quicker recovery from power cycles.</t>
+          <t>Enhanced user experience for non-English speakers, increased adoption.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Printers should be ready to use within seconds after power-on.</t>
+          <t>Users should be able to select their preferred language during setup.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All enterprise printer models.</t>
+          <t>Support at least 5 major languages in firmware UI for Victoria platforms.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Boot time reduced by 20% compared to previous firmware.</t>
+          <t>Firmware UI available in English, Spanish, French, German, and Chinese.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Boot time under 30 seconds for all models.</t>
+          <t>Seamless language switching and localization.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Firmware optimization; hardware readiness; QA testing</t>
+          <t>Firmware UI framework; translation assets</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Firmware Engineering; QA Team</t>
+          <t>Localization Team; Firmware UI Developers</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -780,59 +780,59 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{"errorMessages":["You do not have permission to create issues in this project."],"errors":{}}</t>
+          <t>{"errorMessages":[],"errors":{"labels":"The label 'User Interface' can't contain spaces."}}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Add Multi-Language Support for Printer UI</t>
+          <t>Enable Secure Boot Support in Firmware</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maria Lopez</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Localization</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Enable multi-language support in printer user interface, covering top 5 languages used in target markets.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Expands market reach and improves accessibility for global users.</t>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with enterprise security standards.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Better user satisfaction and reduced support calls in non-English regions.</t>
+          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Users can select their preferred language during setup or from settings.</t>
+          <t>System startup should be seamless and secure, with no noticeable delay for end users.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>All printers shipped to international markets.</t>
+          <t>Implement Secure Boot in firmware for all Victoria platform devices.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Support for English, Spanish, French, German, and Japanese.</t>
+          <t>Secure Boot enabled and verified on all Victoria devices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Support for 10 languages in UI.</t>
+          <t>100% Secure Boot coverage across Victoria platform.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -842,85 +842,85 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Localization files; UI firmware updates</t>
+          <t>Trusted Platform Module (TPM); Firmware signing infrastructure</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Localization Team; Firmware Engineering</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>SCRUM-25419</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25419</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>{"errorMessages":["You do not have permission to create issues in this project."],"errors":{}}</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Implement Energy Saving Mode</t>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alex Kim</t>
+          <t>Emily Chen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sustainability</t>
+          <t>Update &amp; Maintenance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Add firmware-controlled energy saving mode that reduces power consumption during idle periods.</t>
+          <t>Improve the firmware update mechanism to minimize device downtime during updates.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Supports corporate sustainability goals and reduces operational costs.</t>
+          <t>Ensures business continuity and reduces disruption for end users during firmware updates.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lower energy bills and improved environmental footprint.</t>
+          <t>Shorter update windows, improved user satisfaction, and lower operational impact.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Printers automatically enter energy saving mode when idle.</t>
+          <t>Firmware updates should be fast and unobtrusive, with minimal impact on device availability.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>All enterprise printers.</t>
+          <t>Victoria platform firmware update process.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Energy saving mode reduces idle power by 30%.</t>
+          <t>Firmware update downtime reduced to less than 2 minutes per device.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Idle power consumption below 5W.</t>
+          <t>Achieve seamless firmware updates with less than 1 minute downtime.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Firmware power management; hardware support</t>
+          <t>Firmware update infrastructure; Device management tools</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Firmware Engineering; Sustainability Team</t>
+          <t>Platform Firmware Team; IT Operations</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MUST</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -956,7 +956,359 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{"errorMessages":["You do not have permission to create issues in this project."],"errors":{}}</t>
+          <t>{"errorMessages":[],"errors":{"labels":"The label 'Update &amp; Maintenance' can't contain spaces."}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Add Remote Diagnostics Capability to Firmware</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Integrate remote diagnostics features into firmware to allow support teams to access device health and logs remotely.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Improves support efficiency and reduces time to resolution for customer issues.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Faster troubleshooting, reduced need for onsite visits, and improved customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Support teams should be able to access diagnostics remotely without impacting device performance.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Victoria platform devices with network connectivity.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Remote diagnostics accessible for support teams on Victoria devices.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Comprehensive remote diagnostics with real-time log access.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Network connectivity; Support portal integration</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Support Engineering; Platform Firmware Team</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>SCRUM-25420</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25420</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized code execution, meeting enterprise compliance requirements.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Reduces risk of malware and unauthorized access, increases customer trust in platform security.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>System should boot seamlessly with Secure Boot enabled, without impacting user experience.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot in firmware for all supported hardware platforms.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all target platforms.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Full Secure Boot support with no boot failures on compliant hardware.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Trusted Platform Module (TPM); UEFI firmware updates</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Platform Security Team; Hardware Engineering</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>SCRUM-25421</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25421</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Update &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ensures business continuity and reduces operational disruptions during firmware maintenance.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Faster updates, less downtime, improved customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Users should experience minimal interruption during firmware updates.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Optimize update process for all supported devices; target downtime reduction.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Firmware update downtime reduced by at least 50% compared to previous version.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Achieve less than 2 minutes downtime per update.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Firmware update infrastructure; device management tools</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Firmware Engineering; IT Operations</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>{"errorMessages":[],"errors":{"labels":"The label 'Update &amp; Maintenance' can't contain spaces."}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Add Multi-Language Support to Firmware UI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>User Experience</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Integrate multi-language support into the firmware user interface to accommodate global users.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Expands market reach and improves accessibility for non-English speaking customers.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Enhanced usability and satisfaction for international customers.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Users should be able to select their preferred language during initial setup.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Support at least 5 major languages in firmware UI.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Firmware UI available in English, Spanish, French, German, and Japanese.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Seamless language switching with full UI translation.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Localization resources; UI framework updates</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Localization Team; Firmware UI Developers</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>NICE TO HAVE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>{"errorMessages":[],"errors":{"labels":"The label 'User Experience' can't contain spaces."}}</t>
         </is>
       </c>
     </row>

--- a/jira/jiraTickets.xlsx
+++ b/jira/jiraTickets.xlsx
@@ -593,12 +593,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>SCRUM-25418</t>
+          <t>SCRUM-25476</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25418</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25476</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -681,20 +681,20 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>SCRUM-25477</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25477</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>{"errorMessages":[],"errors":{"labels":"The label 'Update Process' can't contain spaces."}}</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -769,20 +769,20 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>SCRUM-25478</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25478</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>{"errorMessages":[],"errors":{"labels":"The label 'User Interface' can't contain spaces."}}</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>SCRUM-25419</t>
+          <t>SCRUM-25479</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25419</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25479</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -945,20 +945,20 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>SCRUM-25480</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25480</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>{"errorMessages":[],"errors":{"labels":"The label 'Update &amp; Maintenance' can't contain spaces."}}</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>SCRUM-25420</t>
+          <t>SCRUM-25481</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25420</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25481</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>SCRUM-25421</t>
+          <t>SCRUM-25482</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25421</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25482</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1209,20 +1209,20 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+          <t>SCRUM-25483</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25483</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>{"errorMessages":[],"errors":{"labels":"The label 'Update &amp; Maintenance' can't contain spaces."}}</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1297,20 +1297,20 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>SCRUM-25484</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-25484</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>{"errorMessages":[],"errors":{"labels":"The label 'User Experience' can't contain spaces."}}</t>
-        </is>
-      </c>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/jira/jiraTickets.xlsx
+++ b/jira/jiraTickets.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Secure Boot Support in Firmware</t>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -538,37 +538,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are loaded during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized code execution at boot time.</t>
+          <t>Enhances platform security by preventing unauthorized or malicious firmware from executing, aligning with enterprise security requirements.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of malware and unauthorized access, meeting enterprise security requirements.</t>
+          <t>Reduces risk of firmware attacks, improves compliance with industry standards, and increases customer trust in device integrity.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>System should boot securely and transparently for end users.</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot verification in firmware for all supported hardware platforms.</t>
+          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all test platforms.</t>
+          <t>Firmware must reject unsigned images and log failure.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% Secure Boot coverage for all Victoria-supported devices.</t>
+          <t>100% of shipped devices enforce Secure Boot for embedded controller firmware.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Firmware cryptographic libraries; hardware TPM support</t>
+          <t>Secure Boot infrastructure; Firmware signing tools; Platform BIOS integration.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Platform Security Team; Hardware Engineering</t>
+          <t>Platform Security Team; Embedded Controller Firmware Team; BIOS Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -593,12 +593,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>SCRUM-25476</t>
+          <t>SCRUM-27554</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25476</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-27554</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+          <t>Optimize Power Consumption During Sleep Mode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -621,42 +621,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Update Process</t>
+          <t>Power Management</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+          <t>Reduce power draw of the platform during sleep mode by optimizing firmware routines and hardware interactions.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ensures business continuity and reduces impact on end users during firmware maintenance.</t>
+          <t>Improves battery life and meets regulatory requirements for energy efficiency.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Faster updates, less disruption, improved user satisfaction.</t>
+          <t>Longer battery runtime, lower operational costs, and improved sustainability credentials.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Users should experience minimal interruption during firmware updates.</t>
+          <t>User should experience minimal battery drain when device is in sleep mode.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Update firmware process logic to reduce downtime across all Victoria platforms.</t>
+          <t>Firmware routines related to sleep mode; hardware power states; platform-wide power management.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Firmware update downtime reduced by at least 50% compared to previous release.</t>
+          <t>Sleep mode power consumption ≤ 0.5W.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Achieve less than 2 minutes downtime per update.</t>
+          <t>Sleep mode power consumption ≤ 0.3W.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Firmware update subsystem; platform power management</t>
+          <t>Hardware power states; Power management IC; OS sleep triggers.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Engineering; QA</t>
+          <t>Power Management Firmware Team; Hardware Engineering; OS Integration Team</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>SCRUM-25477</t>
+          <t>SCRUM-27555</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25477</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-27555</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Add Multi-Language Support to Firmware UI</t>
+          <t>Add Support for Multi-Language Error Messages in Firmware</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -709,42 +709,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Interface</t>
+          <t>Localization</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Integrate multi-language capabilities into the firmware user interface.</t>
+          <t>Implement multi-language support for error messages displayed by firmware during boot and runtime.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Expands market reach and improves accessibility for global users.</t>
+          <t>Improves accessibility and user experience for global customers, reducing support calls and misunderstandings.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enhanced user experience for non-English speakers, increased adoption.</t>
+          <t>Enhanced usability for non-English speakers, broader market reach, and improved customer satisfaction.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Users should be able to select their preferred language during setup.</t>
+          <t>Users should see error messages in their preferred language as configured in system settings.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Support at least 5 major languages in firmware UI for Victoria platforms.</t>
+          <t>Firmware error message handling; language selection logic; integration with system locale settings.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Firmware UI available in English, Spanish, French, German, and Chinese.</t>
+          <t>Support for English, French, German, and Spanish error messages.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Seamless language switching and localization.</t>
+          <t>Support for 10+ languages with dynamic selection based on system locale.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Firmware UI framework; translation assets</t>
+          <t>Localization files; System locale detection; Translation resources.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Localization Team; Firmware UI Developers</t>
+          <t>Firmware Localization Team; QA; Translation Services</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SCRUM-25478</t>
+          <t>SCRUM-27556</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25478</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-27556</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -783,534 +783,6 @@
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Enable Secure Boot Support in Firmware</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Enhances platform security by preventing unauthorized code execution, aligning with enterprise security standards.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>System startup should be seamless and secure, with no noticeable delay for end users.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Implement Secure Boot in firmware for all Victoria platform devices.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Secure Boot enabled and verified on all Victoria devices.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>100% Secure Boot coverage across Victoria platform.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Trusted Platform Module (TPM); Firmware signing infrastructure</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Security Engineering; Platform Firmware Team</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>SCRUM-25479</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25479</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Optimize Firmware Update Process for Reduced Downtime</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Emily Chen</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Update &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Improve the firmware update mechanism to minimize device downtime during updates.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ensures business continuity and reduces disruption for end users during firmware updates.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Shorter update windows, improved user satisfaction, and lower operational impact.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Firmware updates should be fast and unobtrusive, with minimal impact on device availability.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Victoria platform firmware update process.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Firmware update downtime reduced to less than 2 minutes per device.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Achieve seamless firmware updates with less than 1 minute downtime.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Firmware update infrastructure; Device management tools</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Platform Firmware Team; IT Operations</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>SCRUM-25480</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25480</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Add Remote Diagnostics Capability to Firmware</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Raj Patel</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Integrate remote diagnostics features into firmware to allow support teams to access device health and logs remotely.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Improves support efficiency and reduces time to resolution for customer issues.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Faster troubleshooting, reduced need for onsite visits, and improved customer satisfaction.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Support teams should be able to access diagnostics remotely without impacting device performance.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Victoria platform devices with network connectivity.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Remote diagnostics accessible for support teams on Victoria devices.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Comprehensive remote diagnostics with real-time log access.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Network connectivity; Support portal integration</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Support Engineering; Platform Firmware Team</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>SCRUM-25481</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25481</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Enable Secure Boot Support in Firmware</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Enhances platform security by preventing unauthorized code execution, meeting enterprise compliance requirements.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Reduces risk of malware and unauthorized access, increases customer trust in platform security.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>System should boot seamlessly with Secure Boot enabled, without impacting user experience.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Implement Secure Boot in firmware for all supported hardware platforms.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Secure Boot enabled and verified on all target platforms.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Full Secure Boot support with no boot failures on compliant hardware.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Trusted Platform Module (TPM); UEFI firmware updates</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Platform Security Team; Hardware Engineering</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>SCRUM-25482</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25482</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Optimize Firmware Update Process for Reduced Downtime</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Emily Chen</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Update &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ensures business continuity and reduces operational disruptions during firmware maintenance.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Faster updates, less downtime, improved customer satisfaction.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Users should experience minimal interruption during firmware updates.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Optimize update process for all supported devices; target downtime reduction.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Firmware update downtime reduced by at least 50% compared to previous version.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Achieve less than 2 minutes downtime per update.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Firmware update infrastructure; device management tools</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Firmware Engineering; IT Operations</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>WANT</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>SCRUM-25483</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25483</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Add Multi-Language Support to Firmware UI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Carlos Ruiz</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>User Experience</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Integrate multi-language support into the firmware user interface to accommodate global users.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Expands market reach and improves accessibility for non-English speaking customers.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Enhanced usability and satisfaction for international customers.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Users should be able to select their preferred language during initial setup.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Support at least 5 major languages in firmware UI.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Firmware UI available in English, Spanish, French, German, and Japanese.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Seamless language switching with full UI translation.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Localization resources; UI framework updates</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Localization Team; Firmware UI Developers</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>NICE TO HAVE</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>SCRUM-25484</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-25484</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/jira/jiraTickets.xlsx
+++ b/jira/jiraTickets.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>What is it?</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Strategic Importance of Solution</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>New Threshold (Acceptable to Ship)</t>
+          <t>threshold</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -481,40 +481,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Impacted Programs</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Partners</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Partners</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Jira_Ticket_Key</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Jira_Ticket_Key</t>
+          <t>Jira_Ticket_URL</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Jira_Ticket_URL</t>
+          <t>Jira_Status</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Jira_Status</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Jira_Error</t>
         </is>
@@ -573,40 +568,35 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Secure Boot infrastructure; Firmware signing tools; Platform BIOS integration.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Secure Boot infrastructure; Firmware signing tools; Platform BIOS integration.</t>
+          <t>Platform Security Team; Embedded Controller Firmware Team; BIOS Team</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Platform Security Team; Embedded Controller Firmware Team; BIOS Team</t>
+          <t>High</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>SCRUM-27564</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>SCRUM-27554</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-27564</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-27554</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -661,40 +651,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Hardware power states; Power management IC; OS sleep triggers.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Hardware power states; Power management IC; OS sleep triggers.</t>
+          <t>Power Management Firmware Team; Hardware Engineering; OS Integration Team</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Power Management Firmware Team; Hardware Engineering; OS Integration Team</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>SCRUM-27565</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>SCRUM-27555</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-27565</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-27555</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -749,40 +734,35 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Localization files; System locale detection; Translation resources.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Localization files; System locale detection; Translation resources.</t>
+          <t>Firmware Localization Team; QA; Translation Services</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Firmware Localization Team; QA; Translation Services</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SCRUM-27566</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SCRUM-27556</t>
+          <t>https://aavademo.atlassian.net/browse/SCRUM-27566</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-27556</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/jira/jiraTickets.xlsx
+++ b/jira/jiraTickets.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,93 +413,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Requestors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Value Proposition</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Experience Intent (if any)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Partners</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Jira_Ticket_Key</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Jira_Ticket_URL</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Jira_Status</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Jira_Error</t>
         </is>
       </c>
     </row>
@@ -578,25 +556,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SCRUM-27564</t>
+          <t>SCRUM-29112</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-27564</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -661,25 +633,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SCRUM-27565</t>
+          <t>SCRUM-29113</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-27565</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -744,25 +710,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SCRUM-27566</t>
+          <t>SCRUM-29114</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://aavademo.atlassian.net/browse/SCRUM-27566</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
